--- a/docs/design/mp-k8s-오브젝트-시방서(전체)_2026-08-03.xlsx
+++ b/docs/design/mp-k8s-오브젝트-시방서(전체)_2026-08-03.xlsx
@@ -22,6 +22,7 @@
     <sheet name="11.관측" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="12.CD·GitOps" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="13.백업" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="14.배포전략(카나리)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체목록'!$A$1:$I$163</definedName>
@@ -74,7 +75,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +119,12 @@
         <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF7E0"/>
+        <bgColor rgb="00FEF7E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -145,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +191,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -797,13 +807,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>162</v>
+      <c r="B28" s="2" t="n">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4017,13 +4037,273 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>파트</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>네임스페이스</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>종류(Kind)</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>목적/역할</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>핵심 설정</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>생성 출처</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>argo-rollouts</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Helm Release + CRD 5종</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>argo-rollouts</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>카나리 컨트롤러 — 트래픽 분할·자동 분석 엔진(2개 서비스만)</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>v2.41.1(appVer 1.9.1)·컨트롤러 HA2·대시보드·ServiceMonitor · gatewayAPI 플러그인(vendored 이미지)+argo-rollouts-config CM(file://+sha256)+ClusterRole httproutes get/list/update/patch</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>platform/argocd/rollouts.yaml</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>step1 컨트롤러 라이브(2026-08-03) · 플러그인 배선 config #106 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Rollout (argoproj.io/v1alpha1)</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>account · recipe</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Deployment→Rollout 전환(핵심 2개만 카나리, 나머지 7개는 롤링 유지)</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>strategy.canary: setWeight 10→pause{analysis}→50→pause{analysis}→100 · scaleTargetRef→Rollout(HPA min2/max4 유지) · PDB app:&lt;svc&gt; 라벨 그대로 유효</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>services/{account,recipe}/base</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>ADR-0001 §6.4 · recipe 파일럿→account 복제</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>account-canary · recipe-canary</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>카나리 파드 대상 Service(canaryService)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>stableService=기존 Service 재사용 · canaryService=신규 · 플러그인이 HTTPRoute weight 로 stable/canary 트래픽 분할</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>services/{account,recipe}/base</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>ADR-0001 §6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>AnalysisTemplate (argoproj.io)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>mp-canary-analysis</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>카나리 단계별 자동 분석 → 임계 위반 시 abort/롤백</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Istio 텔레메트리: istio_requests_total(5xx&lt;0.05) · istio_request_duration(p95&lt;2000ms) — k6 임계값 정렬</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>services/{account,recipe}/base</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>ADR-0001 §6.5 · Prometheus 이미 라이브(도입비용 0)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6898,7 +7178,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>recipebook·recipe·chat·mealplan(+expenses)·notify·ocr·pantry·account·price·frontend(SPA)</t>
+          <t>recipebook·recipe·chat·mealplan(+expenses)·notify·ocr·pantry·account·price·frontend(SPA) · ⏳S6: account·recipe backendRefs weight(stable/canary)</t>
         </is>
       </c>
     </row>
@@ -11503,6 +11783,194 @@
       <c r="I163" s="11" t="inlineStr">
         <is>
           <t>JCasC 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>argo-rollouts</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>Helm Release + CRD 5종</t>
+        </is>
+      </c>
+      <c r="E164" s="9" t="inlineStr">
+        <is>
+          <t>argo-rollouts</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>카나리 컨트롤러 — 트래픽 분할·자동 분석 엔진(2개 서비스만)</t>
+        </is>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>v2.41.1(appVer 1.9.1)·컨트롤러 HA2·대시보드·ServiceMonitor · gatewayAPI 플러그인(vendored 이미지)+argo-rollouts-config CM(file://+sha256)+ClusterRole httproutes get/list/update/patch</t>
+        </is>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>platform/argocd/rollouts.yaml</t>
+        </is>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>step1 컨트롤러 라이브(2026-08-03) · 플러그인 배선 config #106 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>Rollout (argoproj.io/v1alpha1)</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>account · recipe</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Deployment→Rollout 전환(핵심 2개만 카나리, 나머지 7개는 롤링 유지)</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>strategy.canary: setWeight 10→pause{analysis}→50→pause{analysis}→100 · scaleTargetRef→Rollout(HPA min2/max4 유지) · PDB app:&lt;svc&gt; 라벨 그대로 유효</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>services/{account,recipe}/base</t>
+        </is>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>ADR-0001 §6.4 · recipe 파일럿→account 복제</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="inlineStr">
+        <is>
+          <t>account-canary · recipe-canary</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>카나리 파드 대상 Service(canaryService)</t>
+        </is>
+      </c>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>stableService=기존 Service 재사용 · canaryService=신규 · 플러그인이 HTTPRoute weight 로 stable/canary 트래픽 분할</t>
+        </is>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>services/{account,recipe}/base</t>
+        </is>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>ADR-0001 §6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>14.배포전략(카나리)</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>AnalysisTemplate (argoproj.io)</t>
+        </is>
+      </c>
+      <c r="E167" s="9" t="inlineStr">
+        <is>
+          <t>mp-canary-analysis</t>
+        </is>
+      </c>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>카나리 단계별 자동 분석 → 임계 위반 시 abort/롤백</t>
+        </is>
+      </c>
+      <c r="G167" s="9" t="inlineStr">
+        <is>
+          <t>Istio 텔레메트리: istio_requests_total(5xx&lt;0.05) · istio_request_duration(p95&lt;2000ms) — k6 임계값 정렬</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>services/{account,recipe}/base</t>
+        </is>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>ADR-0001 §6.5 · Prometheus 이미 라이브(도입비용 0)</t>
         </is>
       </c>
     </row>
@@ -14612,7 +15080,7 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>recipebook·recipe·chat·mealplan(+expenses)·notify·ocr·pantry·account·price·frontend(SPA)</t>
+          <t>recipebook·recipe·chat·mealplan(+expenses)·notify·ocr·pantry·account·price·frontend(SPA) · ⏳S6: account·recipe backendRefs weight(stable/canary)</t>
         </is>
       </c>
     </row>
